--- a/470/food/kp2026.xlsx
+++ b/470/food/kp2026.xlsx
@@ -551,8 +551,10 @@
           <t>Год</t>
         </is>
       </c>
-      <c r="AD1" s="15" t="n">
-        <v>2026</v>
+      <c r="AD1" s="15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="AE1" s="17" t="n"/>
       <c r="AF1" s="1" t="n"/>
